--- a/resources/survey_data/sera_aims/case.xlsx
+++ b/resources/survey_data/sera_aims/case.xlsx
@@ -17,9 +17,10 @@
     <sheet name="Photos" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Connections" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Openings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="MasonryTypes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Measured" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="_lists" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Measured" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,122 +202,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Name, the same as the IFC material</t>
+        <t>Facade whose wall has it</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Description</t>
+        <t>FMO vulnerability</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit dimensions</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: unit shape</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: unit material</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: mortar quality</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: horizontal joints</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: vertical joints</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: wall connections</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit dimensions</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit shape</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit material</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for mortar quality</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for horizontal joints</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for vertical joints</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for wall connections</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t>General evidence (optional)</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>Assumptions and caveats, one per line</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>Mass density (HMO has no rule for it)</t>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t>Source of the density</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>Code category it is compared with (optional)</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>Note on the comparison (optional)</t>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
-      <text>
-        <t>Lower variant, as parameter=value; ... (optional)</t>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
-      <text>
-        <t>Upper variant, as parameter=value; ... (optional)</t>
+        <t>What shows it, and its source</t>
       </text>
     </comment>
   </commentList>
@@ -324,6 +220,136 @@
 </file>
 
 <file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>openBIMtoFEM</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Name, the same as the IFC material</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Description</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit dimensions</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit shape</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit material</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: mortar quality</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: horizontal joints</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: vertical joints</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: wall connections</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit dimensions</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit shape</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit material</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for mortar quality</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for horizontal joints</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for vertical joints</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for wall connections</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>General evidence (optional)</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Assumptions and caveats, one per line</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Mass density (HMO has no rule for it)</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Source of the density</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Code category it is compared with (optional)</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Note on the comparison (optional)</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Lower variant, as parameter=value; ... (optional)</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Upper variant, as parameter=value; ... (optional)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>openBIMtoFEM</author>
@@ -1176,6 +1202,541 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>facade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Facade_1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Facade_1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Facade_1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Facade_2_U2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Facade_3_U2</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Facade_4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Facade_4</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Facade_4</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Facade_4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Facade_4</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Facade_5</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Facade_5</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the top of the walls: the beams were simply supported on them, and the connections of steel angles and bearing plates were added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Facade_5</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Timber beams of 8 × 16 cm with a single layer of 2 cm planks nailed to them, a flexible diaphragm (Tomić et al. 2024a, Section 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Facade_5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Facade_5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>No tie rods and no ring beam at the first-floor level of unit 2: the beams were simply supported on the walls, and their connection was added only in the strengthened configuration (Tomić et al. 2024a, Sections 2.3 and 2.4).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_lists!$L$2:$L$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1474,7 +2035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1848,13 +2409,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,6 +2474,11 @@
           <t>yes/no</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1970,6 +2536,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2027,6 +2598,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2079,6 +2655,11 @@
           <t>Tie</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -2101,6 +2682,11 @@
           <t>Document</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -2113,6 +2699,11 @@
           <t>Publication</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -2125,6 +2716,11 @@
           <t>BuildingInformationModel</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ExcessiveSlenderness</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -2132,11 +2728,21 @@
           <t>squared_hard_stone</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OpeningsNearIntersections</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
           <t>irregular_hard_stone</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PresenceOfHorizontalThrust</t>
         </is>
       </c>
     </row>

--- a/resources/survey_data/sera_aims/case.xlsx
+++ b/resources/survey_data/sera_aims/case.xlsx
@@ -613,6 +613,11 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>Name of its masonry type (MasonryTypes)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>GlobalIds of its IFC elements, separated by ; (set by the editor)</t>
       </text>
     </comment>
   </commentList>
@@ -1049,7 +1054,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The half-scale stone masonry aggregate tested on the shake table within the SERA-AIMS project, the benchmark of this thesis, described with the Historic Survey (HSV), Historic Structure (HSTO) and Historic Masonry (HMO) ontologies: the publications and the BIM model, the units, façades and the interface between them, and the mechanical properties of the masonry derived by a reasoner from its published description, next to the measured ones.</t>
+          <t>The half-scale stone masonry aggregate tested on the shake table within the SERA-AIMS project, the benchmark of this thesis, described with the Historic Survey (HSV), Historic Structure (HSTO), Historic Masonry (HMO) and Failure Mechanism (FMO) ontologies: the publications and the BIM model, the units, façades and the interface between them, the mechanical properties of the masonry derived by a reasoner from its published description, next to the measured ones, and the behaviour and expected failure mechanisms of its walls.</t>
         </is>
       </c>
     </row>
@@ -2089,8 +2094,10 @@
           <t>compressive_strength_MPa</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1.37</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -2114,8 +2121,10 @@
           <t>tensile_strength_MPa</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0.21</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -2139,8 +2148,10 @@
           <t>cohesion_MPa</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0.29</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -2164,8 +2175,10 @@
           <t>compressive_strength_MPa</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1.3</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2189,8 +2202,10 @@
           <t>young_modulus_MPa</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>3462</v>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -2214,8 +2229,10 @@
           <t>shear_modulus_MPa</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>1524</v>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1524</t>
+        </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -2239,8 +2256,10 @@
           <t>shear_modulus_MPa</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>1898</v>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -2264,8 +2283,10 @@
           <t>density_kg_m3</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>1980</v>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -2289,8 +2310,10 @@
           <t>compressive_strength_MPa</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>2.74</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2314,8 +2337,10 @@
           <t>young_modulus_MPa</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>6924</v>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2339,8 +2364,10 @@
           <t>shear_modulus_MPa</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>3048</v>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3048</t>
+        </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2364,8 +2391,10 @@
           <t>shear_modulus_MPa</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>3796</v>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2389,8 +2418,10 @@
           <t>shear_strength_turnsek_cacovic_MPa</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>0.28</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -3669,13 +3700,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3699,6 +3731,11 @@
           <t>masonry_type</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>elements</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3721,6 +3758,11 @@
           <t>Double_leaf_stone_masonry</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d_i6</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3743,6 +3785,11 @@
           <t>Double_leaf_stone_masonry</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d_jF</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3765,6 +3812,11 @@
           <t>Double_leaf_stone_masonry</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d_lO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3787,6 +3839,11 @@
           <t>Double_leaf_stone_masonry</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d$U6; 3_2W4VcEf62eVBAFB0d_Xg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3809,6 +3866,11 @@
           <t>Double_leaf_stone_masonry</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d$OL; 3_2W4VcEf62eVBAFB0d_dt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3831,6 +3893,11 @@
           <t>Double_leaf_stone_masonry</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d$PR; 3_2W4VcEf62eVBAFB0d_cf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3851,6 +3918,11 @@
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Double_leaf_stone_masonry</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3_2W4VcEf62eVBAFB0d$Rm; 3_2W4VcEf62eVBAFB0d_ar</t>
         </is>
       </c>
     </row>

--- a/resources/survey_data/sera_aims/case.xlsx
+++ b/resources/survey_data/sera_aims/case.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Project" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Organisations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="People" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Activities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Documents" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Units" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Facades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Photos" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Connections" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Openings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Measured" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organisations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Openings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measured" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -237,37 +237,37 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit dimensions</t>
+        <t>Morphological characteristic: unit dimensions</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit shape</t>
+        <t>Morphological characteristic: unit shape</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit material</t>
+        <t>Morphological characteristic: unit material</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: mortar quality</t>
+        <t>Morphological characteristic: mortar quality</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: horizontal joints</t>
+        <t>Morphological characteristic: horizontal joints</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: vertical joints</t>
+        <t>Morphological characteristic: vertical joints</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: wall connections</t>
+        <t>Morphological characteristic: wall connections</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
@@ -337,12 +337,12 @@
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>Lower variant, as parameter=value; ... (optional)</t>
+        <t>Lower variant, as characteristic=category; ... (optional)</t>
       </text>
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>Upper variant, as parameter=value; ... (optional)</t>
+        <t>Upper variant, as characteristic=category; ... (optional)</t>
       </text>
     </comment>
   </commentList>
@@ -1727,7 +1727,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$L$2:$L$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -2013,25 +2013,25 @@
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$C$2:$C$9</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$D$2:$D$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$E$2:$E$4</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$G$2:$G$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -3558,7 +3558,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$H$2:$H$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -3682,10 +3682,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$I$2:$I$4</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$K$2:$K$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -4226,7 +4226,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$J$2:$J$4</formula1>
     </dataValidation>
   </dataValidations>
